--- a/optimized_version/metadata/validation_daily_metrics/agus2_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus2_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01781537055446069</v>
+        <v>0.02304328706466383</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02224129650741702</v>
+        <v>0.02876799999999946</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02224129650741702</v>
+        <v>0.02876799999999946</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>1.352805815171122</v>
+        <v>1.354071754263073</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.714906157460189</v>
+        <v>1.716537833333334</v>
       </c>
       <c r="F3" t="n">
-        <v>2.979414475578293</v>
+        <v>2.979877168314268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7029823508005777</v>
+        <v>0.7028900920155674</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>3.8111230985977</v>
+        <v>3.81183597225157</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.779765941375617</v>
+        <v>3.780309833333332</v>
       </c>
       <c r="F4" t="n">
-        <v>7.829033872600446</v>
+        <v>7.829050678054182</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7237061876222234</v>
+        <v>0.7237050014610851</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>1.618048833650592</v>
+        <v>1.617648756243546</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.637484058624382</v>
+        <v>1.636940166666667</v>
       </c>
       <c r="F5" t="n">
-        <v>5.093910127646308</v>
+        <v>5.09438410883484</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1906012796657721</v>
+        <v>0.1904506458279471</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>0.08072087252220396</v>
+        <v>0.07923751724487915</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0886480092064789</v>
+        <v>0.08701633333333329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.105219618147906</v>
+        <v>0.1047178230165877</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5558420239305841</v>
+        <v>-0.5410377061861795</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08583583706626756</v>
+        <v>0.08683245029257758</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09396521608457083</v>
+        <v>0.09505300000000123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1166484134570652</v>
+        <v>0.1183562272294962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8729183269179814</v>
+        <v>0.869169959093802</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>4.648398231359666</v>
+        <v>4.650226857981138</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3.90615615746019</v>
+        <v>3.907787833333336</v>
       </c>
       <c r="F8" t="n">
-        <v>10.62665024706988</v>
+        <v>10.62764324719733</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4561000308633316</v>
+        <v>0.4559983773863814</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>1.689519963927218</v>
+        <v>1.690406318866744</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.747469382751233</v>
+        <v>1.748557166666664</v>
       </c>
       <c r="F9" t="n">
-        <v>7.045561329134322</v>
+        <v>7.044041315209187</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09090903711755471</v>
+        <v>-0.09043838106056068</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07495284517743529</v>
+        <v>0.07396386883952977</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08212228391543223</v>
+        <v>0.08103450000000183</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1133002710350467</v>
+        <v>0.1113401220315502</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7566574274296768</v>
+        <v>0.7650044797159026</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>0.092926813377815</v>
+        <v>0.09302425709643032</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1024333333333344</v>
+        <v>0.1025390000000008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1230592362221928</v>
+        <v>0.1217531429738072</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3451895155064639</v>
+        <v>0.3590154582167573</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08687122744542861</v>
+        <v>0.08795596654355758</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09589438275123581</v>
+        <v>0.09708783333333255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1145041207155312</v>
+        <v>0.114301144237491</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.173833624245035</v>
+        <v>-1.166133534340299</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06270708669048794</v>
+        <v>0.06369722562762237</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06913604941790179</v>
+        <v>0.07022383333333219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08431056583197581</v>
+        <v>0.08427446948710615</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5888489938472602</v>
+        <v>0.589200975152935</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8815563074746834</v>
+        <v>0.8810443020784678</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9275798919577145</v>
+        <v>0.9270359999999993</v>
       </c>
       <c r="F14" t="n">
-        <v>2.165764617955262</v>
+        <v>2.165737258444723</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7980629163902476</v>
+        <v>0.7980680183896284</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>3.670166143811485</v>
+        <v>3.669733083752042</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3.70268822529105</v>
+        <v>3.702144333333332</v>
       </c>
       <c r="F15" t="n">
-        <v>8.934184101694065</v>
+        <v>8.933564130141864</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6166929396953209</v>
+        <v>0.6167461356503541</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>12.83194543393022</v>
+        <v>12.83305367034847</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.288016666666667</v>
+        <v>8.288016666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>19.57737756240929</v>
+        <v>19.57738711806789</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4983105518907247</v>
+        <v>0.4983100621444095</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1117905291036843</v>
+        <v>0.1127680509417484</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1445902160845721</v>
+        <v>0.1458503333333342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1914877259898446</v>
+        <v>0.1910499703149211</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1132661358481318</v>
+        <v>0.1173157853256942</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4014057154572727</v>
+        <v>0.4026995827384727</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5106311648719603</v>
+        <v>0.5122629266790147</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9504532457991034</v>
+        <v>0.9517758692652983</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8126067002599073</v>
+        <v>0.812084795099913</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4914235521563819</v>
+        <v>0.4917797820869613</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5815458190142468</v>
+        <v>0.5819931647070072</v>
       </c>
       <c r="F19" t="n">
-        <v>1.603048435646994</v>
+        <v>1.604627830254124</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8873329714807037</v>
+        <v>0.8871108529803602</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>3.197352738464737</v>
+        <v>3.198398763004948</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3.354769382867648</v>
+        <v>3.355857171672522</v>
       </c>
       <c r="F20" t="n">
-        <v>5.021154824468723</v>
+        <v>5.021392874613561</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2615945959963155</v>
+        <v>0.2615245795613425</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>1.273812459573593</v>
+        <v>1.274734401377034</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.428015216084567</v>
+        <v>1.429103000077608</v>
       </c>
       <c r="F21" t="n">
-        <v>3.214912780123026</v>
+        <v>3.214179353864987</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5573446064423061</v>
+        <v>0.5575465516140121</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>1.31888994490919</v>
+        <v>1.318932645465373</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -997,10 +997,10 @@
         <v>1.391583333333334</v>
       </c>
       <c r="F22" t="n">
-        <v>3.924258709821113</v>
+        <v>3.924897156008823</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2873170811640238</v>
+        <v>0.28708516643083</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>5.431106828397622</v>
+        <v>5.433132131598706</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.94645199079352</v>
+        <v>4.948083666666665</v>
       </c>
       <c r="F23" t="n">
-        <v>8.954865418028207</v>
+        <v>8.95490847779533</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2901103077761685</v>
+        <v>0.2901034807035333</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8596359695102973</v>
+        <v>0.8591727176590511</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9015548919577144</v>
+        <v>0.9010109999999992</v>
       </c>
       <c r="F24" t="n">
-        <v>2.370380562013255</v>
+        <v>2.370631468861693</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03287584905750018</v>
+        <v>0.0326710963528638</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>0.3219609429660325</v>
+        <v>0.3209493868056976</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.349318117248765</v>
+        <v>0.3482303333333346</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9806668781378196</v>
+        <v>0.9793482032406402</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1197212695410468</v>
+        <v>-0.1167119793802882</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>0.3121344563242361</v>
+        <v>0.3126399453097999</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3440617747089512</v>
+        <v>0.3446056666666664</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3953643671204051</v>
+        <v>0.3956517174536202</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2398257305871072</v>
+        <v>0.2387203415970168</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8231680037056958</v>
+        <v>0.8217173642966548</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8790771758731483</v>
+        <v>0.8774455000000027</v>
       </c>
       <c r="F27" t="n">
-        <v>2.536507868341116</v>
+        <v>2.536405800990646</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9670236237518124</v>
+        <v>-0.9668653235527929</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7572659263317196</v>
+        <v>0.7578971804699685</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7564617747089516</v>
+        <v>0.7571113333333344</v>
       </c>
       <c r="F28" t="n">
-        <v>1.780381132117535</v>
+        <v>1.782987561404734</v>
       </c>
       <c r="G28" t="n">
-        <v>0.854024581903202</v>
+        <v>0.853596861006504</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7799927637670852</v>
+        <v>0.7777167640188652</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.834698734497526</v>
+        <v>0.8325231666666651</v>
       </c>
       <c r="F29" t="n">
-        <v>3.427076971218131</v>
+        <v>3.425742770783295</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.05397581350725145</v>
+        <v>-0.05315532346709739</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8352620650326282</v>
+        <v>0.8352151833166961</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8812444999999993</v>
+        <v>0.8812445000000005</v>
       </c>
       <c r="F30" t="n">
-        <v>1.910448961225901</v>
+        <v>1.910344453669198</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8039970016462443</v>
+        <v>0.8040184450185787</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.005897999619232147</v>
+        <v>1.070559794881523e-15</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006526703492582442</v>
+        <v>1.1842378929335e-15</v>
       </c>
       <c r="F31" t="n">
-        <v>0.006526703492582442</v>
+        <v>4.102320397618269e-15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9361710209956975</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>0.104124666392819</v>
+        <v>0.1046189652790231</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1150076080422811</v>
+        <v>0.1155514999999963</v>
       </c>
       <c r="F32" t="n">
-        <v>0.134556467032364</v>
+        <v>0.1349661408428036</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5602185917457747</v>
+        <v>0.5575365772799334</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>0.09054336105768657</v>
+        <v>0.09104114703026148</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09973677470895244</v>
+        <v>0.1002806666666676</v>
       </c>
       <c r="F33" t="n">
-        <v>0.131823845585124</v>
+        <v>0.1322623421424248</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4707072629729895</v>
+        <v>0.467180146052702</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1090519381729334</v>
+        <v>0.1080676548740444</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1197806172487628</v>
+        <v>0.1186928333333324</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1474624152179653</v>
+        <v>0.147340301820875</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6831342780723071</v>
+        <v>0.6836588528072953</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>4.961657900396141</v>
+        <v>4.962506195677651</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>4.08494094137562</v>
+        <v>4.085484833333335</v>
       </c>
       <c r="F35" t="n">
-        <v>13.04958098893621</v>
+        <v>13.04957483320462</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.04992611438366357</v>
+        <v>-0.04992512384430015</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>1.264691880101761</v>
+        <v>1.265234836241971</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.388611774708951</v>
+        <v>1.389155666666667</v>
       </c>
       <c r="F36" t="n">
-        <v>3.440874373538303</v>
+        <v>3.441637133737958</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3972514003394876</v>
+        <v>-0.3978709439607244</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3085151789118478</v>
+        <v>0.3079823599280506</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.318546558624383</v>
+        <v>0.3180026666666678</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7238823554543538</v>
+        <v>0.7220518882952011</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8950086625423369</v>
+        <v>0.8955389702886755</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>2.348495253474796</v>
+        <v>2.348568180075264</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1413,10 +1413,10 @@
         <v>2.339475</v>
       </c>
       <c r="F38" t="n">
-        <v>4.134062211065285</v>
+        <v>4.135669362786472</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8605915973643941</v>
+        <v>0.8604831838991102</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>1.345854086752439</v>
+        <v>1.342145655922735</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.374712685079625</v>
+        <v>1.371449333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>4.271076864461633</v>
+        <v>4.269111325009455</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9127702751327615</v>
+        <v>0.9128505424844527</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>0.4941238208791048</v>
+        <v>0.495058409967471</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5807235494178998</v>
+        <v>0.5818113333333302</v>
       </c>
       <c r="F40" t="n">
-        <v>1.398772978937474</v>
+        <v>1.397275573031559</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8376678835393671</v>
+        <v>0.8380152550783888</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4950887615906114</v>
+        <v>0.4950948073707986</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1491,10 +1491,10 @@
         <v>0.5605375000000006</v>
       </c>
       <c r="F41" t="n">
-        <v>1.083963146377563</v>
+        <v>1.08601812617194</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6884363511608439</v>
+        <v>0.6872539052345064</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2192019580369029</v>
+        <v>0.2177321920420725</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2423521758731499</v>
+        <v>0.2407205000000043</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2979728719809932</v>
+        <v>0.2966667507614153</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2599274069225079</v>
+        <v>0.2664011908054096</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3207568923195956</v>
+        <v>0.3195199109342117</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.363985509206478</v>
+        <v>0.3626011666666654</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7533304801302363</v>
+        <v>0.7521525864082829</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8575531212085358</v>
+        <v>0.8579982276103136</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>0.390774595909608</v>
+        <v>0.391799161218561</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4330985493791021</v>
+        <v>0.4341863333333376</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8241687606966309</v>
+        <v>0.825599994422643</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9173762028634265</v>
+        <v>0.9170889882799038</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2469558183404948</v>
+        <v>0.2454830458949991</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2724480092064792</v>
+        <v>0.2708163333333336</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3441890460410729</v>
+        <v>0.3432525320965134</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3325125363407873</v>
+        <v>0.3361399665740905</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>0.532109124436269</v>
+        <v>0.5335892271253604</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5519519907935191</v>
+        <v>0.5535836666666647</v>
       </c>
       <c r="F46" t="n">
-        <v>1.034198953381214</v>
+        <v>1.037033783003556</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9538956829805219</v>
+        <v>0.9536425846567776</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1775247487940596</v>
+        <v>0.1753648348331435</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1785612344975279</v>
+        <v>0.1763856666666671</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2271199373554363</v>
+        <v>0.2256167108704493</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5101160216118581</v>
+        <v>0.516579298875802</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>4.614634597641897</v>
+        <v>4.616438458310141</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>3.800178441375621</v>
+        <v>3.80124466666667</v>
       </c>
       <c r="F48" t="n">
-        <v>10.28826199091207</v>
+        <v>10.28801701318856</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7263563838142597</v>
+        <v>0.7263694153237774</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>0.2287385904006026</v>
+        <v>0.2298965046791998</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2505485494179016</v>
+        <v>0.2518086666666661</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3445869721398261</v>
+        <v>0.3461470797084183</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6370802106265376</v>
+        <v>0.6337865537598194</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5531334034600879</v>
+        <v>0.5525108350446933</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5617514505821024</v>
+        <v>0.5611110000000057</v>
       </c>
       <c r="F50" t="n">
-        <v>1.332554316378825</v>
+        <v>1.334173291726879</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8730685981777238</v>
+        <v>0.8727599823976109</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>0.158240893562039</v>
+        <v>0.1586247296633438</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1584624999999965</v>
+        <v>0.1588431666666625</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1942678281014665</v>
+        <v>0.1937334862829128</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.7385016454384461</v>
+        <v>-0.7289511544881304</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>0.4122340733855551</v>
+        <v>0.4113479560907111</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4308639505820982</v>
+        <v>0.4299568333333331</v>
       </c>
       <c r="F52" t="n">
-        <v>0.855007737445016</v>
+        <v>0.853602467159431</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6116917684420329</v>
+        <v>0.6129671477489131</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3065510561374387</v>
+        <v>0.3070951348001652</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3112742747089522</v>
+        <v>0.3118181666666675</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8563336696933213</v>
+        <v>0.8578332602011509</v>
       </c>
       <c r="G53" t="n">
-        <v>0.284349422203469</v>
+        <v>0.2818407681189588</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>0.7019709668999542</v>
+        <v>0.7013627406128652</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6596632278133837</v>
+        <v>0.6591666282302112</v>
       </c>
       <c r="F54" t="n">
-        <v>1.346256186991157</v>
+        <v>1.346915760868401</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8493852364287304</v>
+        <v>0.8492376183158623</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1622330314018438</v>
+        <v>0.1616664558712576</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.155234652769377</v>
+        <v>0.1546893416506811</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1928812548383132</v>
+        <v>0.1930826951105482</v>
       </c>
       <c r="G55" t="n">
-        <v>0.09460899142625012</v>
+        <v>0.09271686925949729</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5092972006443309</v>
+        <v>0.5093157396921706</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5188291357778029</v>
+        <v>0.5188290765224041</v>
       </c>
       <c r="F56" t="n">
-        <v>1.025654600705412</v>
+        <v>1.023310346302271</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8055247694097695</v>
+        <v>0.8064127455557197</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>0.3295383836945261</v>
+        <v>0.3316451005833339</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3340595986417802</v>
+        <v>0.3362351696352572</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8592304176349681</v>
+        <v>0.8607051859875129</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6657512419682876</v>
+        <v>0.6646028596099816</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>5.236127051045793</v>
+        <v>5.234894350931405</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>4.130527169741936</v>
+        <v>4.128895482692919</v>
       </c>
       <c r="F58" t="n">
-        <v>10.72403837458155</v>
+        <v>10.72400511680129</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5802009920437299</v>
+        <v>0.580203595831785</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6766769958920651</v>
+        <v>0.6772505192506221</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7205117747089554</v>
+        <v>0.7210946668412935</v>
       </c>
       <c r="F59" t="n">
-        <v>1.845724802582177</v>
+        <v>1.845177051772946</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6555912872388965</v>
+        <v>0.6557956754101529</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2694796782007907</v>
+        <v>0.272145719648914</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2734505175492406</v>
+        <v>0.2761701775333651</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5795644403164201</v>
+        <v>0.5817814787712172</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9090975899030667</v>
+        <v>0.9084007921205817</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1356975493965573</v>
+        <v>0.1367734936063515</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.134953846035278</v>
+        <v>0.1360200192692744</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1723428642549579</v>
+        <v>0.1715026815068329</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.3706782558775692</v>
+        <v>-0.3573465392812873</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1447319451717197</v>
+        <v>0.1441913177060083</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1443507602156432</v>
+        <v>0.1438068873112357</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1738423469753023</v>
+        <v>0.1732809485562857</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4726030025651542</v>
+        <v>0.4760038053320201</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2268496531626301</v>
+        <v>0.2254915975279368</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2319947256276365</v>
+        <v>0.2306083044534487</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4816176632034392</v>
+        <v>0.4798731619184647</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8390848404722309</v>
+        <v>0.8402484535292224</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2798389209886102</v>
+        <v>0.2798398179204977</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2830874998835811</v>
+        <v>0.2830875000388016</v>
       </c>
       <c r="F64" t="n">
-        <v>0.499537516752246</v>
+        <v>0.5012853504695269</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8834798339841619</v>
+        <v>0.8826630218020114</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1231619189319322</v>
+        <v>0.1231646319763034</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1226083331005086</v>
+        <v>0.1226083327124575</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1491189081996165</v>
+        <v>0.1484724897359821</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.6094869626101334</v>
+        <v>-0.5955632144753245</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1604866331875999</v>
+        <v>0.1594039682461039</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1604556565195268</v>
+        <v>0.1593678276289771</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2142805582839579</v>
+        <v>0.2131774048090928</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.656365614091404</v>
+        <v>-0.6393549990305261</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8353923562693535</v>
+        <v>0.8349602970294375</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8051473537646222</v>
+        <v>0.8046875557047303</v>
       </c>
       <c r="F67" t="n">
-        <v>2.393890439586177</v>
+        <v>2.393891850871223</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.071761883167456</v>
+        <v>-1.071764325925387</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1427385097300342</v>
+        <v>0.1427436677655261</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2193,10 +2193,10 @@
         <v>0.1430416666666675</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1909121523743263</v>
+        <v>0.1902467854936505</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.025704162207624</v>
+        <v>-1.011608802602994</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8533350967332176</v>
+        <v>0.8528202752639108</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8244340390278015</v>
+        <v>0.8238901663562247</v>
       </c>
       <c r="F69" t="n">
-        <v>2.359930548900507</v>
+        <v>2.359913035860617</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.9577767050689037</v>
+        <v>-0.957747647862685</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8541002141438474</v>
+        <v>0.8532938588522965</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8276689896263841</v>
+        <v>0.8268276203915784</v>
       </c>
       <c r="F70" t="n">
-        <v>2.425607344379777</v>
+        <v>2.425549549577867</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.070183818852644</v>
+        <v>-1.070085167734518</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1607492299480279</v>
+        <v>0.1607558410789557</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1615000004656585</v>
+        <v>0.1615000002910355</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2034897025094326</v>
+        <v>0.2037129097011113</v>
       </c>
       <c r="G71" t="n">
-        <v>0.09291916579752424</v>
+        <v>0.09092812639054504</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>3.801934671078505</v>
+        <v>3.800465632624439</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3.042168842617425</v>
+        <v>3.040537166375631</v>
       </c>
       <c r="F72" t="n">
-        <v>10.09050748489819</v>
+        <v>10.09047740308146</v>
       </c>
       <c r="G72" t="n">
-        <v>0.6437313880268904</v>
+        <v>0.6437335122394006</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>0.135901237651735</v>
+        <v>0.1364432219151509</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.137361775058201</v>
+        <v>0.1379056577803007</v>
       </c>
       <c r="F73" t="n">
-        <v>0.171170831743967</v>
+        <v>0.1714240596920912</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.08144794031955449</v>
+        <v>-0.08465006777715689</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>2.672197361094796</v>
+        <v>2.670753937284998</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.220555617559203</v>
+        <v>2.219467832033361</v>
       </c>
       <c r="F74" t="n">
-        <v>5.153721512451171</v>
+        <v>5.153758776912718</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7355313453318277</v>
+        <v>0.7355275207877121</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3516353517970063</v>
+        <v>0.3505952658309002</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3648931172487633</v>
+        <v>0.3638053333333329</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7485385846044463</v>
+        <v>0.7466745238661006</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8765085725667258</v>
+        <v>0.8771228599314771</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1520913488900176</v>
+        <v>0.1516233947366909</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1594090586243813</v>
+        <v>0.1589124999999996</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2098232988231945</v>
+        <v>0.2097354217595734</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.002333577059166</v>
+        <v>-1.000656715156913</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1253810176082959</v>
+        <v>0.1247068562862552</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1311181172487655</v>
+        <v>0.1304110000000011</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1583571222167753</v>
+        <v>0.1588679006512446</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.5282853744431253</v>
+        <v>-0.538160195747599</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1571764526055747</v>
+        <v>0.1566595455198973</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1642465586243821</v>
+        <v>0.1637026666666669</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2007390376843774</v>
+        <v>0.2005125512048244</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.8077841958851357</v>
+        <v>-0.803707184201405</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1093222767578331</v>
+        <v>0.1088047903713108</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1141215586243819</v>
+        <v>0.1135776666666667</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1437299027717652</v>
+        <v>0.1437149765705258</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.132037146779499</v>
+        <v>-1.131594350082569</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1684791556916101</v>
+        <v>0.1674446795049626</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1762681172487651</v>
+        <v>0.1751803333333347</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2180236745275951</v>
+        <v>0.2171389136566723</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.7925257861061237</v>
+        <v>-0.7780068243708873</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1446300996183223</v>
+        <v>0.1446324837712586</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2531,10 +2531,10 @@
         <v>0.1512666666666706</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2078274387018667</v>
+        <v>0.2080046824569106</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5312171655584232</v>
+        <v>0.5304172301776571</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1448198917751753</v>
+        <v>0.1447401466945602</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1513632252910497</v>
+        <v>0.1512750000000006</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1825694882127442</v>
+        <v>0.1821538954400914</v>
       </c>
       <c r="G82" t="n">
-        <v>-1.349704045741686</v>
+        <v>-1.339018705313357</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1572855749821713</v>
+        <v>0.1559722794246897</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1645823268462165</v>
+        <v>0.1632041739130462</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2258858117375235</v>
+        <v>0.2260217061096071</v>
       </c>
       <c r="G83" t="n">
-        <v>0.3233165909903351</v>
+        <v>0.3225021518065363</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus2_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus2_validation_daily_metrics.xlsx
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4026995827384727</v>
+        <v>0.4026995097368201</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5122629266790147</v>
+        <v>0.5122628333333292</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9517758692652983</v>
+        <v>0.9517757794682105</v>
       </c>
       <c r="G18" t="n">
-        <v>0.812084795099913</v>
+        <v>0.8120848305583395</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4917797820869613</v>
+        <v>0.4917797833725202</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5819931647070072</v>
+        <v>0.5819931666472625</v>
       </c>
       <c r="F19" t="n">
-        <v>1.604627830254124</v>
+        <v>1.604627815860131</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8871108529803602</v>
+        <v>0.8871108550056591</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>3.198398763004948</v>
+        <v>3.198398758661106</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3.355857171672522</v>
+        <v>3.355857166666663</v>
       </c>
       <c r="F20" t="n">
-        <v>5.021392874613561</v>
+        <v>5.021392874519375</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2615245795613425</v>
+        <v>0.2615245795890455</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>1.274734401377034</v>
+        <v>1.274734401311792</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.429103000077608</v>
+        <v>1.429102999999998</v>
       </c>
       <c r="F21" t="n">
-        <v>3.214179353864987</v>
+        <v>3.214179353856487</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5575465516140121</v>
+        <v>0.5575465516163522</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>1.318932645465373</v>
+        <v>1.318932645465357</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -997,10 +997,10 @@
         <v>1.391583333333334</v>
       </c>
       <c r="F22" t="n">
-        <v>3.924897156008823</v>
+        <v>3.924897156006004</v>
       </c>
       <c r="G22" t="n">
-        <v>0.28708516643083</v>
+        <v>0.2870851664318544</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3079823599280506</v>
+        <v>0.3079823598724284</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3180026666666678</v>
+        <v>0.3180026666084602</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7220518882952011</v>
+        <v>0.7220518882924869</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8955389702886755</v>
+        <v>0.8955389702894608</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>0.7013627406128652</v>
+        <v>0.7013627791825028</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6591666282302112</v>
+        <v>0.6591666641831431</v>
       </c>
       <c r="F54" t="n">
-        <v>1.346915760868401</v>
+        <v>1.346915817692635</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8492376183158623</v>
+        <v>0.8492376055950118</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1616664558712576</v>
+        <v>0.1616570738343248</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1546893416506811</v>
+        <v>0.1546803610623145</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1930826951105482</v>
+        <v>0.1930813758342269</v>
       </c>
       <c r="G55" t="n">
-        <v>0.09271686925949729</v>
+        <v>0.09272926760582412</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5093157396921706</v>
+        <v>0.5093145287205523</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5188290765224041</v>
+        <v>0.518827805907374</v>
       </c>
       <c r="F56" t="n">
-        <v>1.023310346302271</v>
+        <v>1.023302411951647</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8064127455557197</v>
+        <v>0.8064157475447133</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>0.3316451005833339</v>
+        <v>0.3316450975911401</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3362351696352572</v>
+        <v>0.3362351665502512</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8607051859875129</v>
+        <v>0.8607051828171713</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6646028596099816</v>
+        <v>0.6646028620808009</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>5.234894350931405</v>
+        <v>5.234894365249496</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>4.128895482692919</v>
+        <v>4.128895500368645</v>
       </c>
       <c r="F58" t="n">
-        <v>10.72400511680129</v>
+        <v>10.72400509717855</v>
       </c>
       <c r="G58" t="n">
-        <v>0.580203595831785</v>
+        <v>0.5802035973680688</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6772505192506221</v>
+        <v>0.6772505193251124</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7210946668412935</v>
+        <v>0.7210946669189037</v>
       </c>
       <c r="F59" t="n">
-        <v>1.845177051772946</v>
+        <v>1.845177051776818</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6557956754101529</v>
+        <v>0.6557956754087082</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>0.272145719648914</v>
+        <v>0.2721456215276771</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2761701775333651</v>
+        <v>0.2761700800743381</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5817814787712172</v>
+        <v>0.5817814774735143</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9084007921205817</v>
+        <v>0.9084007925292181</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1367734936063515</v>
+        <v>0.136773697454282</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1360200192692744</v>
+        <v>0.1360202239662153</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1715026815068329</v>
+        <v>0.1715033338315052</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.3573465392812873</v>
+        <v>-0.3573568648611849</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1441913177060083</v>
+        <v>0.1441908346296593</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1438068873112357</v>
+        <v>0.1438063924491052</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1732809485562857</v>
+        <v>0.1732730676562193</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4760038053320201</v>
+        <v>0.4760514674411271</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2254915975279368</v>
+        <v>0.2254825894159397</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2306083044534487</v>
+        <v>0.2305991583807021</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4798731619184647</v>
+        <v>0.4798621658080859</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8402484535292224</v>
+        <v>0.8402557747367878</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2798398179204977</v>
+        <v>0.2798398178843787</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2830875000388016</v>
+        <v>0.2830874999999964</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5012853504695269</v>
+        <v>0.5012853501822402</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8826630218020114</v>
+        <v>0.8826630219365031</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1231646319763034</v>
+        <v>0.123164632591366</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1226083327124575</v>
+        <v>0.1226083333333392</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1484724897359821</v>
+        <v>0.1484724916968389</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.5955632144753245</v>
+        <v>-0.5955632566201137</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1594039682461039</v>
+        <v>0.1594039710443939</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1593678276289771</v>
+        <v>0.1593678306169704</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2131774048090928</v>
+        <v>0.2131774002356311</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.6393549990305261</v>
+        <v>-0.639354928689795</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8349602970294375</v>
+        <v>0.8349602615398234</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8046875557047303</v>
+        <v>0.8046875206249133</v>
       </c>
       <c r="F67" t="n">
-        <v>2.393891850871223</v>
+        <v>2.393891833028698</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.071764325925387</v>
+        <v>-1.071764295042199</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1427436677655261</v>
+        <v>0.1427436677268641</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1430416666666675</v>
+        <v>0.1430416666278624</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1902467854936505</v>
+        <v>0.190246785401428</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.011608802602994</v>
+        <v>-1.011608800652732</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8528202752639108</v>
+        <v>0.8528202909494621</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8238901663562247</v>
+        <v>0.8238901817812548</v>
       </c>
       <c r="F69" t="n">
-        <v>2.359913035860617</v>
+        <v>2.359913039800432</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.957747647862685</v>
+        <v>-0.9577476543995032</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8532938588522965</v>
+        <v>0.8532934925251531</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8268276203915784</v>
+        <v>0.8268272494341554</v>
       </c>
       <c r="F70" t="n">
-        <v>2.425549549577867</v>
+        <v>2.425549490053177</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.070085167734518</v>
+        <v>-1.070085066131831</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1607558410789557</v>
+        <v>0.1607558407845217</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1615000002910355</v>
+        <v>0.1614999999999972</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2037129097011113</v>
+        <v>0.2037129094845623</v>
       </c>
       <c r="G71" t="n">
-        <v>0.09092812639054504</v>
+        <v>0.09092812832325081</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>3.800465632624439</v>
+        <v>3.800465632893569</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3.040537166375631</v>
+        <v>3.040537166666669</v>
       </c>
       <c r="F72" t="n">
-        <v>10.09047740308146</v>
+        <v>10.09047740295476</v>
       </c>
       <c r="G72" t="n">
-        <v>0.6437335122394006</v>
+        <v>0.6437335122483472</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1364432219151509</v>
+        <v>0.1364432306447157</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1379056577803007</v>
+        <v>0.1379056666084626</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1714240596920912</v>
+        <v>0.171424066565341</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.08465006777715689</v>
+        <v>-0.08465015475527471</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>2.670753937284998</v>
+        <v>2.670753938530566</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.219467832033361</v>
+        <v>2.219467833294527</v>
       </c>
       <c r="F74" t="n">
-        <v>5.153758776912718</v>
+        <v>5.153758776915955</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7355275207877121</v>
+        <v>0.7355275207873798</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
